--- a/data/trans_camb/IP16A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 9,38</t>
+          <t>-14,62; 10,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 0,0</t>
+          <t>-23,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 1,73</t>
+          <t>-20,84; 1,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 9,18</t>
+          <t>-5,89; 11,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 23,89</t>
+          <t>-2,58; 22,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 2,39</t>
+          <t>-11,48; 2,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 6,03</t>
+          <t>-7,8; 6,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,33</t>
+          <t>-6,71; 9,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 0,7</t>
+          <t>-10,51; 1,06</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,53</t>
+          <t>-9,98; 6,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 12,01</t>
+          <t>-6,55; 12,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 0,0</t>
+          <t>-16,01; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 0,0</t>
+          <t>-18,14; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 18,04</t>
+          <t>-7,01; 15,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 0,0</t>
+          <t>-15,06; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 4,82</t>
+          <t>-6,76; 6,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 12,1</t>
+          <t>-4,61; 12,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 0,0</t>
+          <t>-11,61; 0,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 14,45</t>
+          <t>-19,76; 14,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 10,8</t>
+          <t>-25,15; 10,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 0,0</t>
+          <t>-30,94; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 11,83</t>
+          <t>-18,24; 10,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,61; -2,67</t>
+          <t>-26,12; -2,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 21,56</t>
+          <t>-16,15; 21,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 8,47</t>
+          <t>-14,43; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 1,87</t>
+          <t>-18,25; 0,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 11,31</t>
+          <t>-13,63; 11,7</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 441,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 538,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 573,19</t>
+          <t>-100,0; 395,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 8,13</t>
+          <t>-9,56; 8,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 3,09</t>
+          <t>-12,68; 3,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 1,41</t>
+          <t>-14,32; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 7,94</t>
+          <t>-5,84; 8,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 3,03</t>
+          <t>-8,99; 3,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 6,36</t>
+          <t>-7,09; 6,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,94</t>
+          <t>-5,05; 5,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 1,77</t>
+          <t>-7,99; 2,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 1,71</t>
+          <t>-7,49; 2,27</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,3; 493,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 277,18</t>
+          <t>-67,28; 276,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 106,13</t>
+          <t>-90,04; 154,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,45; 98,09</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 0,0</t>
+          <t>-14,08; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 6,75</t>
+          <t>-10,13; 6,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 4,04</t>
+          <t>-21,47; 4,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 3,75</t>
+          <t>-21,26; 3,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,72; -3,02</t>
+          <t>-25,62; -2,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 0,63</t>
+          <t>-13,84; 0,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 0,17</t>
+          <t>-14,31; 0,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -0,72</t>
+          <t>-15,2; -0,36</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 211,21</t>
+          <t>-100,0; 112,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 33,84</t>
+          <t>-16,83; 29,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 0,0</t>
+          <t>-35,15; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 0,0</t>
+          <t>-35,15; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-47,38; -5,9</t>
+          <t>-45,44; -5,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 22,91</t>
+          <t>-32,28; 21,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 9,36</t>
+          <t>-35,79; 10,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-29,12; -0,36</t>
+          <t>-30,45; -0,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 6,03</t>
+          <t>-27,29; 6,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 4,37</t>
+          <t>-29,05; 3,16</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 411,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 2,92</t>
+          <t>-5,92; 3,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -0,77</t>
+          <t>-8,65; -0,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,23</t>
+          <t>-8,95; -0,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 0,55</t>
+          <t>-8,41; 0,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 2,81</t>
+          <t>-7,16; 3,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 0,5</t>
+          <t>-8,87; 0,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,66</t>
+          <t>-6,07; 0,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,37</t>
+          <t>-6,35; 0,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,24; -1,06</t>
+          <t>-7,42; -1,23</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 83,52</t>
+          <t>-69,9; 90,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-94,47; 9,05</t>
+          <t>-92,8; 12,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-97,02; -15,0</t>
+          <t>-94,81; -2,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-82,31; 18,23</t>
+          <t>-83,2; 23,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-70,8; 73,91</t>
+          <t>-73,09; 71,53</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,58; 20,07</t>
+          <t>-82,69; 14,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 16,64</t>
+          <t>-69,05; 12,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 10,96</t>
+          <t>-73,62; 6,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,52; -19,86</t>
+          <t>-82,35; -20,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 10,42</t>
+          <t>-15,67; 9,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 0,0</t>
+          <t>-24,73; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 1,68</t>
+          <t>-20,78; 1,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 11,06</t>
+          <t>-5,94; 9,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 22,2</t>
+          <t>-2,39; 24,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 2,4</t>
+          <t>-11,81; 2,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 6,22</t>
+          <t>-7,99; 6,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 9,51</t>
+          <t>-6,08; 9,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 1,06</t>
+          <t>-10,78; 0,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 6,48</t>
+          <t>-9,64; 6,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 12,19</t>
+          <t>-6,45; 15,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 0,0</t>
+          <t>-16,74; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 0,0</t>
+          <t>-19,42; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 15,34</t>
+          <t>-3,85; 18,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 0,0</t>
+          <t>-18,38; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 6,25</t>
+          <t>-6,81; 5,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 12,48</t>
+          <t>-5,04; 12,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 0,0</t>
+          <t>-11,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 14,88</t>
+          <t>-20,48; 14,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 10,76</t>
+          <t>-24,96; 10,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 0,0</t>
+          <t>-32,18; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 10,29</t>
+          <t>-17,35; 10,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,12; -2,65</t>
+          <t>-25,45; -2,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 21,63</t>
+          <t>-13,24; 21,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 9,15</t>
+          <t>-14,74; 6,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 0,79</t>
+          <t>-18,63; 0,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 11,7</t>
+          <t>-14,33; 12,62</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 441,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 538,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 395,5</t>
+          <t>-100,0; 390,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 8,66</t>
+          <t>-9,55; 8,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 3,33</t>
+          <t>-12,51; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 1,37</t>
+          <t>-15,15; 1,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 8,21</t>
+          <t>-5,98; 8,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 3,38</t>
+          <t>-9,74; 1,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 6,45</t>
+          <t>-6,88; 5,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 5,47</t>
+          <t>-5,09; 6,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,1</t>
+          <t>-8,0; 1,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 2,27</t>
+          <t>-7,13; 1,92</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-81,3; 493,38</t>
+          <t>-87,0; 431,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 276,04</t>
+          <t>-70,46; 278,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-90,04; 154,25</t>
+          <t>-100,0; 138,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,71; 104,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 0,0</t>
+          <t>-15,6; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 0,0</t>
+          <t>-16,37; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 6,77</t>
+          <t>-10,39; 6,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 4,32</t>
+          <t>-22,15; 3,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 3,89</t>
+          <t>-22,11; 3,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -2,91</t>
+          <t>-27,39; -3,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 0,71</t>
+          <t>-14,53; 0,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 0,29</t>
+          <t>-15,13; 0,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -0,36</t>
+          <t>-15,77; -0,18</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 112,04</t>
+          <t>-100,0; 139,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 29,71</t>
+          <t>-16,65; 30,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 0,0</t>
+          <t>-41,31; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 0,0</t>
+          <t>-41,31; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-45,44; -5,91</t>
+          <t>-45,53; -5,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 21,5</t>
+          <t>-31,12; 25,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 10,19</t>
+          <t>-38,66; 10,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-30,45; -0,06</t>
+          <t>-30,15; 1,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 6,61</t>
+          <t>-26,67; 5,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 3,16</t>
+          <t>-26,57; 4,08</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 411,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,25</t>
+          <t>-6,37; 3,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -0,45</t>
+          <t>-8,6; -0,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -0,89</t>
+          <t>-8,54; -0,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 0,41</t>
+          <t>-8,07; 0,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 3,01</t>
+          <t>-6,97; 3,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,19</t>
+          <t>-8,38; 0,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 0,62</t>
+          <t>-5,75; 0,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 0,07</t>
+          <t>-6,19; -0,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -1,23</t>
+          <t>-7,29; -1,59</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-69,9; 90,15</t>
+          <t>-73,86; 109,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-92,8; 12,15</t>
+          <t>-94,07; 2,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-94,81; -2,98</t>
+          <t>-93,59; 3,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-83,2; 23,28</t>
+          <t>-81,66; 24,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-73,09; 71,53</t>
+          <t>-71,56; 71,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 14,74</t>
+          <t>-80,94; 27,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-69,05; 12,66</t>
+          <t>-68,92; 7,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,62; 6,15</t>
+          <t>-74,15; -1,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,35; -20,45</t>
+          <t>-82,99; -28,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-7,25</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,41</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-5,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>-3,4</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 9,45</t>
+          <t>-5,83; 9,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 0,0</t>
+          <t>-2,87; 23,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 1,74</t>
+          <t>-11,82; 2,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 9,09</t>
+          <t>-16,6; 9,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 24,53</t>
+          <t>-22,6; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 2,54</t>
+          <t>-22,06; 1,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 6,68</t>
+          <t>-7,47; 6,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 9,13</t>
+          <t>-7,53; 9,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 0,73</t>
+          <t>-10,79; 0,44</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>257,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-61,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-21,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-76,59%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>257,25%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-56,86%</t>
+          <t>-79,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-69,22%</t>
+          <t>-72,53%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,6</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,6</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-3,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-3,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,63</t>
+          <t>-19,56; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 15,28</t>
+          <t>-7,15; 18,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 0,0</t>
+          <t>-18,78; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 0,0</t>
+          <t>-9,64; 6,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 18,45</t>
+          <t>-6,57; 12,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 0,0</t>
+          <t>-13,28; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 5,19</t>
+          <t>-6,75; 4,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 12,03</t>
+          <t>-4,53; 12,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 0,0</t>
+          <t>-11,78; 0,0</t>
         </is>
       </c>
     </row>
@@ -946,27 +946,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104,97%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-0,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18,77%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>104,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-9,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,67</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,88</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-10,02</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,69</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-4,06</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,64</t>
+          <t>-4,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 14,3</t>
+          <t>-17,38; 11,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 10,78</t>
+          <t>-25,61; -2,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 0,0</t>
+          <t>-14,65; 16,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 10,72</t>
+          <t>-20,82; 14,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -2,63</t>
+          <t>-25,25; 10,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 21,25</t>
+          <t>-30,37; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 6,88</t>
+          <t>-14,25; 8,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 0,41</t>
+          <t>-17,82; 1,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 12,62</t>
+          <t>-15,87; 6,67</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-46,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-13,85%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-36,59%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-48,68%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-46,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-41,47%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-26,91%</t>
+          <t>-47,86%</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 390,41</t>
+          <t>-100,0; 499,4</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,57</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,72</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-1,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 8,11</t>
+          <t>-5,9; 7,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 2,82</t>
+          <t>-10,51; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 1,25</t>
+          <t>-6,52; 7,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 8,69</t>
+          <t>-9,03; 8,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 1,98</t>
+          <t>-12,39; 3,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 5,94</t>
+          <t>-12,32; 5,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 6,22</t>
+          <t>-5,11; 5,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 1,89</t>
+          <t>-8,08; 1,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,92</t>
+          <t>-6,07; 3,67</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-51,72%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-0,2%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-53,01%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-70,16%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-51,72%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>-44,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-43,27%</t>
+          <t>-21,48%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 431,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-70,46; 278,0</t>
+          <t>-68,67; 277,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 138,07</t>
+          <t>-100,0; 106,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-88,71; 104,02</t>
+          <t>-78,92; 218,04</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-7,04</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-8,37</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-11,85</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-3,33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,33</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-7,04</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-8,37</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-11,85</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,64</t>
+          <t>-7,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 0,0</t>
+          <t>-23,13; 4,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 0,0</t>
+          <t>-23,1; 3,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 6,48</t>
+          <t>-26,72; -3,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 3,81</t>
+          <t>-15,36; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 3,77</t>
+          <t>-17,97; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,39; -3,06</t>
+          <t>-13,68; 4,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 0,34</t>
+          <t>-14,83; 0,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 0,22</t>
+          <t>-14,87; 0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -0,18</t>
+          <t>-16,49; -1,71</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-59,43%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-70,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-2,34%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-59,43%</t>
-        </is>
-      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-70,68%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-32,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-82,08%</t>
+          <t>-86,88%</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,58</t>
+          <t>-100,0; 211,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-19,78</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,48</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-9,38</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>1,38</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-8,24</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-8,24</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-19,78</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,48</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-10,21</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>-11,94</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-9,87</t>
+          <t>-9,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 30,27</t>
+          <t>-47,38; -5,9</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 0,0</t>
+          <t>-31,95; 22,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 0,0</t>
+          <t>-39,43; 11,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-45,53; -5,91</t>
+          <t>-16,7; 33,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 25,8</t>
+          <t>-35,2; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-38,66; 10,78</t>
+          <t>-35,2; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 1,12</t>
+          <t>-29,12; -0,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 5,86</t>
+          <t>-25,96; 6,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 4,08</t>
+          <t>-26,6; 4,75</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-22,63%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-47,42%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>16,71%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-22,63%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-51,64%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>-78,58%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-64,99%</t>
+          <t>-63,62%</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-3,73</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-4,09</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,31</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,09</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,38</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-3,73</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-4,19</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,18</t>
+          <t>-4,15</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 3,22</t>
+          <t>-7,91; 0,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -0,4</t>
+          <t>-7,4; 2,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,64</t>
+          <t>-8,32; 0,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 0,67</t>
+          <t>-6,13; 2,92</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,05</t>
+          <t>-8,86; -0,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 0,91</t>
+          <t>-8,86; -0,74</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 0,25</t>
+          <t>-5,99; 0,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -0,19</t>
+          <t>-6,29; 0,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -1,59</t>
+          <t>-7,27; -1,23</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-51,39%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-27,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-56,25%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-21,74%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-67,85%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-72,6%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-51,39%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-27,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-53,34%</t>
+          <t>-69,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-62,3%</t>
+          <t>-61,87%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 109,7</t>
+          <t>-82,31; 18,23</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-94,07; 2,46</t>
+          <t>-70,8; 73,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-93,59; 3,04</t>
+          <t>-82,4; 11,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,66; 24,15</t>
+          <t>-70,58; 83,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-71,56; 71,92</t>
+          <t>-94,47; 9,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 27,93</t>
+          <t>-95,08; -2,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-68,92; 7,13</t>
+          <t>-68,58; 16,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-74,15; -1,0</t>
+          <t>-73,4; 10,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,99; -28,54</t>
+          <t>-82,74; -22,58</t>
         </is>
       </c>
     </row>
